--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-27T18:29:33Z by SETUP | data d41a1ff52fdd8904</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-27T18:48:52Z by SETUP | data f16a494a971dde84</t>
         </is>
       </c>
     </row>
@@ -2493,6 +2493,297 @@
 contract_clause/ALP-EPC-001_A4</t>
         </is>
       </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TQ-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Reference fuel LHV inconsistent with the reference composition</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>ER-03.02 and DP-CASE-0018 give LHV 48.4 MJ/kg for the reference composition. ISO 6976 gives 47.48 MJ/kg (34.78 MJ/Sm3, relative density 0.598) for that composition; ALP-OWN-FUL-001 section 3 itself gives 34.4 MJ/Sm3 and relative density 0.600, which also mean about 47 MJ/kg. Guarantees are on heat input, so the error does not change them, but fuel flow, the gas booking check and the metering design use the mass LHV.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Correct ER-03.02 and DP-CASE-0018 to 47.48 MJ/kg (ISO 6976, 25 degC combustion reference).</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-03.02
+design_parameter:DP-CASE-0018
+source:SRC-OWNR-0003</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TQ-026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>i_and_c</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Power island control system: integration solution for SC-013</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>IEC's turbine control system keeps its own controllers (turbine protection) with the HMI integration package: graphics and alarms native on the plant DCS operator stations, one KKS tag database, common time sync, own IEC 62443 zone (TQ-IEC-004). Does the Owner accept this as 'integrated in the DCS' under SC-013?</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Accept as compliant with SC-013.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>scope_item:SC-013
+requirement:ER-12.01</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TQ-027</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>electrical</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Export above the 640 MW connection capacity in winter</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Below about 5 degC the plant can export more than 640 MW (about 670 MW net at -4.8 degC). The TCS provides an export limiter at the HV metering point. Please confirm the export limit to be set (640 MW net at the 380 kV meters?) and whether the Owner intends to increase the connection capacity.</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Limiter set to 640 MW net.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter:DP-OWNR-0051
+requirement:ER-18.02</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TQ-028</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>mechanical</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Hot gas path interval: EOH basis and calendar interval</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>ER-05.07 requires a hot gas path interval of at least 25,000 EOH. With the OEM start factors (hot 10, warm 15, cold 20 EOH) and the ER-01.03 regime this is about 2.3 calendar years. Please confirm that ER-05.07 is EOH-based as written.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Confirm the EOH basis; OEM start factors per TQ-IEC-010.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-05.07
+requirement:ER-01.03</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TQ-029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Scope item SC-011 still states a 60 m stack</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>TQ-007 agreed a 65 m stack and ER-06.06 was revised, but the scope split item SC-011 (Appendix D) still reads "Stack 60 m with CEMS platform and silencer". Please confirm the editorial correction before signature.</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>SC-011: Stack 65 m with CEMS platform and silencer (per TQ-007 / ER-06.06).</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>scope_item:SC-011
+requirement:ER-06.06</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
@@ -2507,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2602,74 +2893,83 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Round 4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B6" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="D6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>1480000</v>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>owner to provide</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>price adjustment</t>
+          <t>none</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2679,20 +2979,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>owner to provide</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>price adjustment</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B15" t="n">
         <v>2</v>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-27T18:48:52Z by SETUP | data f16a494a971dde84</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:17:00Z by SETUP | data 697afb309489c934</t>
         </is>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:17:00Z by SETUP | data 697afb309489c934</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:43:27Z by SETUP | data 739c56375ca05fc7</t>
         </is>
       </c>
     </row>
@@ -2657,17 +2657,37 @@
 requirement:ER-18.02</t>
         </is>
       </c>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="4" t="n"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>The export limiter shall be set to 640 MW net at the 380 kV revenue meters. The Owner has applied to the TSO for a connection capacity of 680 MW; if granted, the Owner will instruct the new set point as a variation.</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr"/>
-      <c r="O31" s="4" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
       <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>tie_in/TP-E1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2784,6 +2804,259 @@
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TQ-030</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Tie-in register: confirmation of the terminal point conditions</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>The Consortium's tie-in register (draft) states for each terminal point the exact scope break, connection, isolation, protection, operating envelope, capacity and the dates needed from the Contractor's commissioning sequence. Please confirm, and provide the missing data: (a) TP-W1 maximum supply pressure; (b) TP-E2 prospective short-circuit current of the 34.5 kV supply; (c) SC-001 (site boundary) has no terminal point - propose TP-A2 plot handover incl. the 11 kV cable relocation by 2027-06-30; (d) SC-035 and SC-038 need Owner/TSO/authority input - propose TP-T3 (TSO SCADA and metering link) and TP-T2 (emission data link to the Ministry); (e) TP-A1 is available on 2027-03-01, the day it is needed (no float): earlier access requested.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Confirm the draft; TP-W1 6 barg max; add TP-A2, TP-T2, TP-T3; TP-A1 from 2027-02-01.</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>tie_in:TP-W1
+tie_in:TP-E2
+tie_in:TP-A1
+scope_item:SC-001
+scope_item:SC-035
+scope_item:SC-038
+source:SRC-OWNR-0005</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Register confirmed with: (a) TP-W1 2.5-6.0 barg; (b) TP-E2 12.5 kA; (c) TP-A2 added (plot, 11 kV cable relocated by 2027-06-30, east strip E 370-400 until then not available); (d) TP-T2 and TP-T3 added; (e) TP-A1 lease from 2027-02-01. The conditions of all terminal points TP-A1..TP-W1 are agreed.</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>tie_in/TP-A1
+tie_in/TP-A2
+tie_in/TP-CW1
+tie_in/TP-CW2
+tie_in/TP-D1
+tie_in/TP-E1
+tie_in/TP-E2
+tie_in/TP-G1
+tie_in/TP-L1
+tie_in/TP-M1
+tie_in/TP-R1
+tie_in/TP-S1
+tie_in/TP-T1
+tie_in/TP-T2
+tie_in/TP-T3
+tie_in/TP-W1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TQ-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>electrical</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Short-circuit level at TP-E1: plant contribution</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>ALP-OWN-ELE-001 gives 40 kA (2029) and 50 kA (2035 planning) at the plant 380 kV busbar; the GIS is specified for 50 kA (ER-11.01). The Alpilla generators add about 3.7 kA (GT 2.4 kA, ST 1.3 kA). Please confirm whether the TSO values include the Alpilla contribution; if not, 50 kA would be exceeded in 2035.</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>TSO to confirm that 50 kA includes the Alpilla units.</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>tie_in:TP-E1
+requirement:ER-11.01
+source:SRC-OWNR-0006</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>The TSO confirms (letter of 2026-09-25) that 40 kA (2029) and 50 kA (2035) include the contribution of the Alpilla units. The GIS rating of 50 kA stands.</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>confirmed as is</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>tie_in/TP-E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TQ-032</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>electrical</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Reactive capability: generator terminals (ER-04.08) or connection point (ELE-001)</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>ER-04.08 requires 0.85 lagging / 0.95 leading at rated active power at the generator terminals; ALP-OWN-ELE-001 section 3 states the same at the connection point. At the connection point, at the winter GT output of 470 MW, the GT generator and GSU would need about 600 MVA instead of 560 MVA (GSU reactive losses). Please confirm that ER-04.08 governs.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>ER-04.08 governs (generator terminals); the connection agreement requirement is met with the plant's reactive capability less the GSU losses.</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-04.08
+tie_in:TP-E1
+tie_in:IF-34
+source:SRC-OWNR-0006</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>ER-04.08 governs: 0.85 lagging / 0.95 leading at rated active power at the generator terminals. The TSO accepts the Grid Code compliance demonstration on that basis; ALP-OWN-ELE-001 will be corrected in its next revision.</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>confirmed as is</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
@@ -2798,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2902,94 +3175,103 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Round 5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="B7" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>1480000</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>owner to provide</t>
+          <t>none</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>price adjustment</t>
+          <t>owner to provide</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2999,20 +3281,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>price adjustment</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>2</v>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:43:27Z by SETUP | data 739c56375ca05fc7</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:56:48Z by SETUP | data 86fb906a41f93ae0</t>
         </is>
       </c>
     </row>
@@ -3057,6 +3057,92 @@
       </c>
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TQ-033</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Appendix A.19 (codes and standards) and the permits register</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>ER-01.07 sets the order of precedence and refers to 'the codes and standards listed in Appendix A.19', but the Contract has no Appendix A.19. The Consortium proposes the attached register (Turkish laws and regulations, Grid Code, codes and standards, each with edition, responsible party and the ER it serves) as Appendix A.19, and the permits register with applicant, supporting deliverables, lead times and need dates. Please confirm: (a) the register as Appendix A.19, editions at the Base Date; (b) the EIA limits (ER-14.02) govern over the Large Combustion Plants Regulation where stricter; (c) the permit split: the Owner applies for and holds the development, permanent-works and operating permits (SC-003), the Contractor for its construction permits; (d) permits PMT-005, PMT-007, PMT-014 have less than 14 days float between approval and need - earlier applications requested; (e) dates of PMT-001 and PMT-002.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>(a)-(c) as proposed; (d) Owner applications 30 days earlier; PMT-007: Contractor's barge landing design by 2027-03-31.</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-01.07
+requirement:ER-14.02
+scope_item:SC-003
+permit:PMT-005
+permit:PMT-007
+permit:PMT-014</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>(a) Agreed: the register (with ISO 14001 added by the Owner) is Appendix A.19; editions at the Base Date. (b) Confirmed: the stricter EIA limits of ER-14.02 govern. (c) Confirmed. (d) The Owner applies for PMT-005 on 2026-11-16, PMT-007 on 2027-04-01 (Contractor's design by 2027-03-31) and PMT-014 on 2028-03-15; the Contractor advances its own applications likewise. (e) PMT-001 granted 2026-03-12, PMT-002 granted 2026-05-28.</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>permit/PMT-001
+permit/PMT-002
+permit/PMT-005
+permit/PMT-007
+permit/PMT-014</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
@@ -3191,10 +3277,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -3210,10 +3296,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>4</v>
@@ -3255,7 +3341,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:56:48Z by SETUP | data 86fb906a41f93ae0</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T15:04:30Z by SETUP | data 8002a4a11746e259</t>
         </is>
       </c>
     </row>
@@ -2541,17 +2541,38 @@
 source:SRC-OWNR-0003</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="4" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Agreed. The 48.4 MJ/kg was a rounded network operator figure on another reference basis. ER-03.02 and DP-CASE-0018 are corrected to 47.48 MJ/kg (ISO 6976, 25 degC combustion reference); guarantees remain on heat input at the reference composition.</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr"/>
-      <c r="O29" s="4" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>requirement changed</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
       <c r="P29" s="4" t="n"/>
-      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>requirement/ER-03.02
+design_parameter/DP-CASE-0018</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2599,17 +2620,37 @@
 requirement:ER-12.01</t>
         </is>
       </c>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="4" t="n"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Accepted as compliant with SC-013 and ER-12.01 on condition that (1) all power island operation, alarms and trends are available on the DCS operator stations with the DCS look and feel (no separate operator HMI needed in normal operation), (2) alarm management follows the plant alarm philosophy (EEMUA 191 / IEC 62682), (3) all TCS signals are archived in the plant historian. SC-013 is reworded accordingly.</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr"/>
-      <c r="O30" s="4" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>scope_item/SC-013</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2735,17 +2776,37 @@
 requirement:ER-01.03</t>
         </is>
       </c>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="4" t="n"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed: ER-05.07 is EOH-based with the OEM start factors (hot 10, warm 15, cold 20 EOH, trips per TQ-IEC-010). The Owner accepts about 2.3 calendar years at the ER-01.03 regime; ER-05.07 is clarified.</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr"/>
-      <c r="O32" s="4" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>confirmed as is</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>requirement/ER-05.07</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2793,17 +2854,37 @@
 requirement:ER-06.06</t>
         </is>
       </c>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="4" t="n"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed: SC-011 corrected to a 65 m stack (TQ-007, ER-06.06).</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr"/>
-      <c r="O33" s="4" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>requirement changed</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>scope_item/SC-011</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3144,6 +3225,164 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>TQ-034</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Aqueous ammonia storage basis (ER-06.04)</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>ER-06.04 requires aqueous ammonia storage for 2 x 7 days at base load. SCR consumption is 125 kg/h on gas and 480 kg/h on LDO (TQ-IEC-018). 7 days on gas is 21 t per tank; 72 h on LDO (the LDO storage autonomy, ER-03.08) needs 34.6 t. Please confirm the basis: 2 x 7 days on gas, and the total also covering 72 h of LDO operation.</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>2 tanks of 30 m3 (27 t of 24.5 % solution each): 7 days on gas per tank, 72 h on LDO from one full and one half-full tank; unloading from 25 t road tankers.</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-06.04
+requirement:ER-03.08
+tie_in:IF-25</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Accepted: 2 x 30 m3 as proposed; ER-06.04 clarified. The ammonia inventory (about 54 t) is added to the major accident notification (PMT-015).</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>requirement/ER-06.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>TQ-035</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Engineering start-up: KKS key list, document numbering, MDL, review classes and AWP definitions</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>(1) ER-17.01 requires the Owner's document numbering, which has not been provided. The consortium proposes ALP-&lt;ORG&gt;-&lt;KKS system or 00000&gt;-&lt;DISC&gt;-&lt;TYPE&gt;-&lt;NNNN&gt; (procedure ALP-EPC-00000-GE-PRC-0002), with the IEC 61355 document class on every document type. Does the Owner accept it as the project numbering? (2) Please approve the project KKS key list (125 function, equipment-unit and component keys, 0 = common / 1 = GT+HRSG / 2 = ST unit numbering) for use in engineering. (3) Please accept the MDL (623 documents incl. the IEC VDRL) as the document baseline, the review classes per document type (approval / review / information / internal) and the Basic Design Package flag (21-day review). (4) Please accept the AWP definitions: 12 CWAs in path-of-construction order, one CWP per CWA and discipline, one EWP per CWP needed 20 working days before the CWP starts, MRs as PWPs (ROS at the first CWP start); IWPs are prepared by the construction contractors from the CWPs.</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Adopt the consortium numbering as the Owner's numbering under ER-17.01; approve the key list with verification by the Owner's Engineer; accept the MDL, review classes and AWP definitions.</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-01.06
+requirement:ER-17.01
+requirement:ER-17.02</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>(1) Accepted: the consortium numbering is the project numbering under ER-17.01; the Owner's EDMS will use it unchanged. (2) The KKS key list is approved for engineering. The Owner's Engineer verifies each key title against the VGB-S-811 key catalogue with the KKS manual review; until then keys stay flagged 'not verified'. (3) MDL accepted as baseline for the Basic Design Package. Review classes accepted with one change: logic diagrams (LOG) incl. cause and effect are safety relevant and are for approval. The MDL is updated monthly with the progress report. (4) AWP definitions accepted. The Owner requires every CWP to be released for construction only when its EWP is complete (all IFC) and its PWP materials are on site or have a confirmed delivery before the planned installation.</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>requirement changed</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>doc_type/LOG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3157,7 +3396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3261,10 +3500,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3290,84 +3529,102 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>1480000</v>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Round 6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Round 7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1480000</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>contractor proposal accepted</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>11</v>
-      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>owner to provide</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>price adjustment</t>
+          <t>owner to provide</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3377,21 +3634,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>price adjustment</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>2</v>
+      <c r="B17" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T15:04:30Z by SETUP | data 8002a4a11746e259</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T17:23:01Z by SETUP | data 2cd2ed22bfcdf89a</t>
         </is>
       </c>
     </row>
@@ -3383,6 +3383,150 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>TQ-036</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>MDL Rev B baseline: document quantities, new document types, structures and packages</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>The consortium re-issues the MDL as Rev B: 2205 documents (1455 EPC, 120 IEC, 630 other suppliers), 21,362 sheets. Rev A (623 documents) missed the per-tag deliverables, the supplier documents of the BOP packages, factory and site tests, system-based commissioning and O&amp;M documents and several permit dossiers. Document quantities now follow rules per system / structure / area / package with estimated quantities until the registers exist. Please accept (1) the MDL Rev B as the document baseline, (2) the new document types TST, TRP, WIR, HUP, SUP, RBR, EFD, MOS, MDB, CEM, HMI with their review classes, (3) the structure keys UZD (pipe racks), UZE (cable trenches), UZF (temporary barge landing), (4) the 14 added procurement packages, (5) the review of supplier documents: EPC reviews all; transmitted to the Owner for approval: supplier P&amp;IDs, ITPs and FAT procedures; for review: GA, datasheets, calculations, schematics, manuals; for information: manufacturing record books.</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-17.01
+requirement:ER-01.06
+requirement:ER-16.01</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>(1)-(5) accepted with one change and one condition. Change: fire fighting, escape route and safety signage drawings are submitted to the fire brigade (occupancy permit PMT-020) and are for Owner approval. Condition: the Owner's Engineer review load must be planned; the consortium issues a monthly document issue forecast (from the engineering plan) and transmits in batches of at most 150 documents per week. The new structure keys are approved for engineering (verification with the KKS key list).</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>requirement changed</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="n"/>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>mdl_rule/DL-HS-ESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>TQ-037</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>AWP release rule: progressive EWP release to the IWPs of a CWP</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>TQ-035 requires a CWP to be released only when its EWP is complete (all documents IFC). With the Rev B MDL a piping CWP carries up to 2,800 isometric sheets and a civil CWP the reinforcement of every pour; requiring all of them IFC before the first IWP would delay construction by 3-9 months or require engineering staff far above a realistic peak. The consortium proposes: (a) a CWP is released when the documents of its first IWPs are IFC (layouts, GA, foundations, plans: 100 % at release) and its materials for those IWPs are on site or confirmed; (b) progressive documents (isometrics, supports, schematics, loop diagrams, reinforcement, equipment foundations) are released per IWP, planned at CWP start - lead + share x CWP duration per document type; (c) no IWP is issued to the field unless all its documents are IFC and its constraints removed; (d) the EWP completeness per CWP is reported monthly.</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-17.02</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Accepted as proposed, with the condition that the monthly report shows per CWP the IFC status of the documents needed for the next 8 weeks of IWPs, and that a CWP whose first-IWP documents are not IFC is not started. TQ-035 item (4) is amended accordingly.</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="n"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3396,7 +3540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3567,74 +3711,83 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Round 8</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="B10" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>1480000</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>6</v>
-      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>owner to provide</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>price adjustment</t>
+          <t>owner to provide</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3644,21 +3797,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>price adjustment</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
+      <c r="B18" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T17:23:01Z by SETUP | data 2cd2ed22bfcdf89a</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T18:13:10Z by SETUP | data ae00813907e24242</t>
         </is>
       </c>
     </row>
@@ -3527,6 +3527,60 @@
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="5" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>TQ-038</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Payment milestone MS-02 (Basic Design Package approved, month 3) cannot be met</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Release gate G-OWN-BDP: The Basic Design Package (25 documents, of them 10 P&amp;IDs) must be approved for MS-02 at month 3 (2027-02-02). With the Owner review period for the BDP (21 days, ER-17.01) and the input chain design basis -&gt; system design specification -&gt; P&amp;ID, the earliest possible approval is 2027-03-08 even with unlimited staff; with the planned process team (12 FTE, 9,000 h of P&amp;IDs needed before May 2027 for the long-lead requisitions and the first EWPs) the BDP is approved on 2027-07-21. Please confirm one of: (a) MS-02 split into MS-02a 'BDP batch 1 approved' (design bases, PFDs, HMB, plot plan, SLD, power island P&amp;IDs; month 5) and MS-02b 'BDP batch 2 approved' (BOP P&amp;IDs; month 9), same total percentage; (b) MS-02 at month 9; (c) approval on the tender-stage P&amp;IDs at IFR with the IFC review later. The consortium recommends (a).</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>contract_clause:ALP-EPC-001_15.3
+requirement:ER-17.01</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3540,7 +3594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3730,97 +3784,126 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Round 9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B11" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="n">
+      <c r="D11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>1480000</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>6</v>
-      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>owner to provide</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>price adjustment</t>
+          <t>none</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>owner to provide</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>price adjustment</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B20" t="n">
         <v>6</v>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T18:13:10Z by SETUP | data ae00813907e24242</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T19:00:23Z by EPCE | data 9f2f099cc0049c68</t>
         </is>
       </c>
     </row>
@@ -3580,6 +3580,60 @@
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>TQ-039</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Owner platform levels below +15.00 m (survey ALP-SUR-TOP-001)</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>The topographic survey (ALP-EPC-00000-CV-RPT-0003) shows the Owner-levelled platform on average 66 mm below the +15.00 m stated in ER-02.01 / ALP-OWN-GEN-001, with 51 of 208 grid points outside +-0.10 m (systematic fall to the south, old warehouse foundations up to +0.25 m). Trimming to +15.00 m needs about 9,300 m3 of structural fill. Please confirm (a) the acceptance tolerance of the Owner platform and whether the fill below -0.10 m is at the Owner cost, or (b) that the Contractor may set the finished floor and road levels on the as-surveyed platform with local trimming only.</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-02.01
+source:SRC-EPCE-0011</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
@@ -3790,13 +3844,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3809,13 +3863,13 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>37</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1480000</v>
@@ -3864,7 +3918,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T19:00:23Z by EPCE | data 9f2f099cc0049c68</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-29T02:54:29Z by SETUP | data 849c15aaf34be70d</t>
         </is>
       </c>
     </row>
@@ -3569,17 +3569,40 @@
 requirement:ER-17.01</t>
         </is>
       </c>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="4" t="n"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Option (a) accepted. MS-02 becomes 'Basic Design Package batch 1 approved and power island order' (4 %, month 5): design bases and design criteria, KKS manual, heat balances, process flow diagrams, key single line diagram, plot plan, power block layouts and DCS architecture. New MS-13 'Basic Design Package batch 2 approved' (4 %, month 9): BOP P&amp;IDs of the gas station, CW pumps, feedwater, main steam, reheat, LP steam and condensate systems. The Owner's Engineer reviews each batch within 21 days of receipt; P&amp;IDs of batch 2 may be submitted progressively.</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>requirement changed</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
       <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>milestone/MS-02
+milestone/MS-13
+gate_rule/G-OWN-BDP
+gate_rule/G-OWN-BDP2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3623,17 +3646,107 @@
 source:SRC-EPCE-0011</t>
         </is>
       </c>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="4" t="n"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>(b) with a limit. The Owner's earthworks contract levelled the platform to +15.00 m +- 0.15 m; the survey shows the platform within that tolerance except the south edge strip (N 0-25 m, 17 points), the old warehouse foundations (2 points; demolition is Contractor scope anyway) and three isolated points 1-3 cm beyond the band. The Contractor sets finished floor and road levels on the as-surveyed platform with local trimming only; structural fill needed below +14.85 m is paid by the Owner at the unit rate of the Price Schedule against a joint survey.</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="inlineStr"/>
-      <c r="O43" s="4" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>price adjustment</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
       <c r="P43" s="4" t="n"/>
       <c r="Q43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>TQ-040</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Firm gas capacity booking has 1 % margin over the plant peak demand</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Peak gas demand is 113,950 Sm3/h (GT 23 kg/s at the maximum case per IF-01 plus the auxiliary boiler and the gas-fired station preheaters), 99 % of the firm booking of 115,000 Sm3/h (DP-OWNR-0033). Please confirm that the Owner will book at least 120,000 Sm3/h firm, or that the auxiliary boiler and the preheaters may be interrupted at GT full load in winter.</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter:DP-OWNR-0033
+tie_in:TP-G1</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>The Owner will increase the firm booking to 120,000 Sm3/h from the first gas date; the network operator has confirmed the capacity is available at the TP-G1 connection.</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>owner to provide</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="n"/>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter/DP-OWNR-0033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
@@ -3648,7 +3761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3844,13 +3957,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
         <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3863,13 +3976,13 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1480000</v>
@@ -3914,51 +4027,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>owner to provide</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>owner to provide</t>
+          <t>price adjustment</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>price adjustment</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>requirement changed</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>requirement changed</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-EPC-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-29T02:54:29Z by SETUP | data 849c15aaf34be70d</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-29T03:49:36Z by EPCE | data 852c90d1bca64236</t>
         </is>
       </c>
     </row>
@@ -3748,6 +3748,153 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>TQ-041</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Design criteria: coastal flood level, chlorine compliance point, CW rise in transients, fire water refill</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>(1) ER-02.09 sets floor levels 0.5 m above the 100-year coastal flood level plus 0.5 m sea-level rise; ALP-OWN-MAR-001 gives storm surge -0.4 / +0.6 m and Hs 50-year 4.4 m but no 100-year flood level or wave run-up. Please provide both. (2) Residual oxidant &lt;= 0.1 mg/l 'at the outfall' (EIA, DP-CASE-0017): please confirm the compliance point (end of pipe at the diffuser, or edge of a mixing zone). (3) The condenser rise &lt;= 7 K (EIA): does it apply to start-up and trip bypass transients (IEC DS-105: 8.8 - 9.5 K)? (4) Fire water: 2 x 100 % tanks of 700 m3 filled from the SWRO permeate; one tank is refilled in about 10 h (NFPA 850: 8 h) while the other holds the full demand - please confirm acceptance by the Owner's insurer.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>(1) Owner data; (2) end of pipe, measured at the outfall seal pit; (3) steady state only; (4) accepted.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-02.09
+source:SRC-OWNR-0002
+source:SRC-OWNR-0007
+design_parameter:DP-CASE-0017
+design_parameter:DP-CASE-0015
+requirement:ER-10.05</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>(1) 100-year still water level +0.90 m (national datum, storm surge and barometric set-up, Owner's marine consultant 2025); with the 0.5 m sea-level rise +1.40 m, so the ER-02.09 minimum floor level is +1.90 m. Wave run-up on the shore revetment (50-year) +4.8 m: structures at the shoreline shall have their floors at least at +5.3 m. (2) The compliance point is the end of the outfall pipe; sampling at the outfall seal pit is accepted as representative (no dilution between seal pit and diffuser); no mixing zone is credited. (3) The 7 K applies to steady-state operation as an hourly mean in all ambient conditions; start-up and trip bypass transients up to 60 min are allowed and reported in the monthly environmental report. (4) Accepted by the insurer on the condition that both tanks have separate suction connections and a low-level alarm to the control room.</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>owner to provide</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="n"/>
+      <c r="Q45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>TQ-042</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>project_control</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Expedited review of the tender-stage Basic Design Package criteria issued late</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>The tender-stage design criteria ALP-EPC-00000-CV-DBR-0001, ALP-EPC-00000-EL-DBR-0001, ALP-EPC-00000-HV-DBR-0001, ALP-EPC-00000-IC-DBR-0001, ALP-EPC-00000-ME-SPC-0001, ALP-EPC-00000-PR-HMB-0001 were planned for first issue at NTP (2026-11-02) and are issued Rev A on 2026-12-14 after TQ-041. With the 21-day BDP review and an IFA cycle their IFC moves to late January 2027 and the civil EWPs of CWA-01/02/03/04/05/06/07/11/12 and the enquiries of MR-EL-009 and MR-PI-002 fall 1 to 23 working days behind their need dates. Please agree a review of 10 working days and acceptance in one review cycle (IFC after incorporation of the comments, no IFA) for these six documents.</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>10 working days review, one cycle (review class 'review') for the six documents.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Withdrawn by the Contractor before use: the analysis showed the late first issue, not the review period, drives the civil path (the downstream documents need these criteria at IFR). The Owner answer of 2026-12-16 is not applied.</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3761,7 +3908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3970,97 +4117,116 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Round 10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="B12" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E12" s="6" t="n">
         <v>1480000</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>6</v>
-      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>owner to provide</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>price adjustment</t>
+          <t>owner to provide</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>price adjustment</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
         <v>7</v>
       </c>
     </row>
